--- a/OLT_BBC_MAP.xlsx
+++ b/OLT_BBC_MAP.xlsx
@@ -1,40 +1,849 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamsh\AppData\Local\Temp\MicrosoftEdgeDownloads\cfa36706-d488-40ce-b4bc-e85430139ad7\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C904E3-24EF-456B-9B61-8D9086EEFA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="263">
+  <si>
+    <t>OLT IP</t>
+  </si>
+  <si>
+    <t>BBC Name</t>
+  </si>
+  <si>
+    <t>SPANDANA T</t>
+  </si>
+  <si>
+    <t>10.215.132.172</t>
+  </si>
+  <si>
+    <t>MAHESHWARAPU RANJITH KUMAR-WDP</t>
+  </si>
+  <si>
+    <t>10.215.132.141</t>
+  </si>
+  <si>
+    <t>KIRAN KUMAR ENUGULA</t>
+  </si>
+  <si>
+    <t>10.215.132.60</t>
+  </si>
+  <si>
+    <t>10.215.132.177</t>
+  </si>
+  <si>
+    <t>A PRAVEEN-JAN</t>
+  </si>
+  <si>
+    <t>10.215.132.163</t>
+  </si>
+  <si>
+    <t>10.215.132.30</t>
+  </si>
+  <si>
+    <t>10.215.132.33</t>
+  </si>
+  <si>
+    <t>VINEETH GUNTI</t>
+  </si>
+  <si>
+    <t>10.215.132.133</t>
+  </si>
+  <si>
+    <t>10.210.49.19</t>
+  </si>
+  <si>
+    <t>10.215.132.145</t>
+  </si>
+  <si>
+    <t>10.215.132.101</t>
+  </si>
+  <si>
+    <t>10.210.49.24</t>
+  </si>
+  <si>
+    <t>10.210.49.25</t>
+  </si>
+  <si>
+    <t>10.210.49.27</t>
+  </si>
+  <si>
+    <t>10.210.49.35</t>
+  </si>
+  <si>
+    <t>10.215.132.217</t>
+  </si>
+  <si>
+    <t>10.210.49.150</t>
+  </si>
+  <si>
+    <t>10.210.49.194</t>
+  </si>
+  <si>
+    <t>10.210.49.69</t>
+  </si>
+  <si>
+    <t>CH MADHUKAR RAO</t>
+  </si>
+  <si>
+    <t>10.215.132.43</t>
+  </si>
+  <si>
+    <t>10.215.132.42</t>
+  </si>
+  <si>
+    <t>10.215.132.198</t>
+  </si>
+  <si>
+    <t>10.215.132.212</t>
+  </si>
+  <si>
+    <t>10.215.132.55</t>
+  </si>
+  <si>
+    <t>VIKRAM NALLA</t>
+  </si>
+  <si>
+    <t>10.215.132.208</t>
+  </si>
+  <si>
+    <t>10.215.132.210</t>
+  </si>
+  <si>
+    <t>10.215.132.92</t>
+  </si>
+  <si>
+    <t>10.215.132.85</t>
+  </si>
+  <si>
+    <t>10.215.132.118</t>
+  </si>
+  <si>
+    <t>10.210.49.34</t>
+  </si>
+  <si>
+    <t>10.215.132.46</t>
+  </si>
+  <si>
+    <t>10.215.132.169</t>
+  </si>
+  <si>
+    <t>10.215.132.106</t>
+  </si>
+  <si>
+    <t>10.215.132.211</t>
+  </si>
+  <si>
+    <t>10.215.132.44</t>
+  </si>
+  <si>
+    <t>10.215.132.223</t>
+  </si>
+  <si>
+    <t>10.215.132.97</t>
+  </si>
+  <si>
+    <t>10.215.132.209</t>
+  </si>
+  <si>
+    <t>10.210.49.29</t>
+  </si>
+  <si>
+    <t>10.210.49.10</t>
+  </si>
+  <si>
+    <t>10.215.132.170</t>
+  </si>
+  <si>
+    <t>10.215.132.38</t>
+  </si>
+  <si>
+    <t>10.215.132.150</t>
+  </si>
+  <si>
+    <t>10.215.132.34</t>
+  </si>
+  <si>
+    <t>10.215.132.157</t>
+  </si>
+  <si>
+    <t>10.210.49.204</t>
+  </si>
+  <si>
+    <t>10.215.132.216</t>
+  </si>
+  <si>
+    <t>10.210.49.15</t>
+  </si>
+  <si>
+    <t>10.215.132.75</t>
+  </si>
+  <si>
+    <t>10.215.132.87</t>
+  </si>
+  <si>
+    <t>10.215.132.94</t>
+  </si>
+  <si>
+    <t>10.210.49.190</t>
+  </si>
+  <si>
+    <t>BHIKSHAPATHI MANCHALA</t>
+  </si>
+  <si>
+    <t>10.215.132.132</t>
+  </si>
+  <si>
+    <t>10.215.132.226</t>
+  </si>
+  <si>
+    <t>10.215.132.144</t>
+  </si>
+  <si>
+    <t>10.215.132.146</t>
+  </si>
+  <si>
+    <t>10.215.132.143</t>
+  </si>
+  <si>
+    <t>10.215.132.129</t>
+  </si>
+  <si>
+    <t>10.215.132.130</t>
+  </si>
+  <si>
+    <t>10.215.132.201</t>
+  </si>
+  <si>
+    <t>10.215.132.142</t>
+  </si>
+  <si>
+    <t>10.215.132.171</t>
+  </si>
+  <si>
+    <t>10.215.132.48</t>
+  </si>
+  <si>
+    <t>10.215.132.151</t>
+  </si>
+  <si>
+    <t>10.210.49.20</t>
+  </si>
+  <si>
+    <t>10.215.132.113</t>
+  </si>
+  <si>
+    <t>10.215.132.89</t>
+  </si>
+  <si>
+    <t>10.215.132.127</t>
+  </si>
+  <si>
+    <t>10.215.132.206</t>
+  </si>
+  <si>
+    <t>10.215.132.140</t>
+  </si>
+  <si>
+    <t>10.215.132.84</t>
+  </si>
+  <si>
+    <t>10.215.132.123</t>
+  </si>
+  <si>
+    <t>10.215.132.120</t>
+  </si>
+  <si>
+    <t>10.210.49.5</t>
+  </si>
+  <si>
+    <t>10.215.132.25</t>
+  </si>
+  <si>
+    <t>10.215.132.117</t>
+  </si>
+  <si>
+    <t>10.215.132.228</t>
+  </si>
+  <si>
+    <t>10.215.132.58</t>
+  </si>
+  <si>
+    <t>10.215.132.69</t>
+  </si>
+  <si>
+    <t>10.215.132.215</t>
+  </si>
+  <si>
+    <t>10.215.132.83</t>
+  </si>
+  <si>
+    <t>10.215.132.77</t>
+  </si>
+  <si>
+    <t>10.215.132.74</t>
+  </si>
+  <si>
+    <t>10.215.132.219</t>
+  </si>
+  <si>
+    <t>10.215.132.173</t>
+  </si>
+  <si>
+    <t>10.215.132.32</t>
+  </si>
+  <si>
+    <t>10.215.132.149</t>
+  </si>
+  <si>
+    <t>10.215.132.218</t>
+  </si>
+  <si>
+    <t>10.215.132.119</t>
+  </si>
+  <si>
+    <t>10.215.132.10</t>
+  </si>
+  <si>
+    <t>10.215.132.104</t>
+  </si>
+  <si>
+    <t>10.215.132.147</t>
+  </si>
+  <si>
+    <t>10.215.132.168</t>
+  </si>
+  <si>
+    <t>10.215.132.15</t>
+  </si>
+  <si>
+    <t>10.215.132.131</t>
+  </si>
+  <si>
+    <t>10.215.132.134</t>
+  </si>
+  <si>
+    <t>10.215.132.165</t>
+  </si>
+  <si>
+    <t>10.210.49.65</t>
+  </si>
+  <si>
+    <t>10.215.132.128</t>
+  </si>
+  <si>
+    <t>A PRAVEEN-CHR</t>
+  </si>
+  <si>
+    <t>10.215.132.16</t>
+  </si>
+  <si>
+    <t>10.210.49.59</t>
+  </si>
+  <si>
+    <t>10.215.132.237</t>
+  </si>
+  <si>
+    <t>10.215.132.160</t>
+  </si>
+  <si>
+    <t>10.210.49.191</t>
+  </si>
+  <si>
+    <t>10.210.49.30</t>
+  </si>
+  <si>
+    <t>10.210.49.70</t>
+  </si>
+  <si>
+    <t>10.210.49.26</t>
+  </si>
+  <si>
+    <t>10.215.132.174</t>
+  </si>
+  <si>
+    <t>10.215.132.176</t>
+  </si>
+  <si>
+    <t>10.215.132.24</t>
+  </si>
+  <si>
+    <t>10.215.132.240</t>
+  </si>
+  <si>
+    <t>10.215.132.189</t>
+  </si>
+  <si>
+    <t>10.215.132.254</t>
+  </si>
+  <si>
+    <t>10.215.132.225</t>
+  </si>
+  <si>
+    <t>10.215.132.224</t>
+  </si>
+  <si>
+    <t>10.215.132.253</t>
+  </si>
+  <si>
+    <t>10.215.132.155</t>
+  </si>
+  <si>
+    <t>10.215.132.80</t>
+  </si>
+  <si>
+    <t>10.215.132.114</t>
+  </si>
+  <si>
+    <t>10.215.132.40</t>
+  </si>
+  <si>
+    <t>10.215.132.99</t>
+  </si>
+  <si>
+    <t>10.215.132.31</t>
+  </si>
+  <si>
+    <t>10.215.132.88</t>
+  </si>
+  <si>
+    <t>10.215.132.79</t>
+  </si>
+  <si>
+    <t>10.215.132.78</t>
+  </si>
+  <si>
+    <t>10.215.132.90</t>
+  </si>
+  <si>
+    <t>10.215.132.236</t>
+  </si>
+  <si>
+    <t>10.215.132.45</t>
+  </si>
+  <si>
+    <t>10.215.132.252</t>
+  </si>
+  <si>
+    <t>10.215.132.20</t>
+  </si>
+  <si>
+    <t>10.215.132.251</t>
+  </si>
+  <si>
+    <t>10.215.132.29</t>
+  </si>
+  <si>
+    <t>10.215.132.164</t>
+  </si>
+  <si>
+    <t>10.210.49.37</t>
+  </si>
+  <si>
+    <t>10.215.132.233</t>
+  </si>
+  <si>
+    <t>10.215.132.232</t>
+  </si>
+  <si>
+    <t>10.215.132.21</t>
+  </si>
+  <si>
+    <t>10.210.49.7</t>
+  </si>
+  <si>
+    <t>10.210.49.4</t>
+  </si>
+  <si>
+    <t>10.215.132.178</t>
+  </si>
+  <si>
+    <t>10.215.132.57</t>
+  </si>
+  <si>
+    <t>10.215.132.200</t>
+  </si>
+  <si>
+    <t>10.215.132.22</t>
+  </si>
+  <si>
+    <t>10.215.132.63</t>
+  </si>
+  <si>
+    <t>10.215.132.95</t>
+  </si>
+  <si>
+    <t>10.215.132.96</t>
+  </si>
+  <si>
+    <t>10.215.132.76</t>
+  </si>
+  <si>
+    <t>10.215.132.185</t>
+  </si>
+  <si>
+    <t>10.215.132.65</t>
+  </si>
+  <si>
+    <t>10.215.132.71</t>
+  </si>
+  <si>
+    <t>10.215.132.67</t>
+  </si>
+  <si>
+    <t>10.215.132.51</t>
+  </si>
+  <si>
+    <t>10.215.132.115</t>
+  </si>
+  <si>
+    <t>10.215.132.50</t>
+  </si>
+  <si>
+    <t>10.215.132.81</t>
+  </si>
+  <si>
+    <t>10.215.132.239</t>
+  </si>
+  <si>
+    <t>10.215.132.124</t>
+  </si>
+  <si>
+    <t>10.215.132.121</t>
+  </si>
+  <si>
+    <t>10.215.132.111</t>
+  </si>
+  <si>
+    <t>10.215.132.227</t>
+  </si>
+  <si>
+    <t>10.215.132.122</t>
+  </si>
+  <si>
+    <t>10.215.132.230</t>
+  </si>
+  <si>
+    <t>10.215.132.126</t>
+  </si>
+  <si>
+    <t>10.215.132.39</t>
+  </si>
+  <si>
+    <t>10.215.132.109</t>
+  </si>
+  <si>
+    <t>10.215.132.70</t>
+  </si>
+  <si>
+    <t>10.215.132.72</t>
+  </si>
+  <si>
+    <t>10.215.132.154</t>
+  </si>
+  <si>
+    <t>10.215.132.82</t>
+  </si>
+  <si>
+    <t>10.215.132.54</t>
+  </si>
+  <si>
+    <t>10.215.132.204</t>
+  </si>
+  <si>
+    <t>10.215.132.53</t>
+  </si>
+  <si>
+    <t>10.215.132.52</t>
+  </si>
+  <si>
+    <t>10.215.132.125</t>
+  </si>
+  <si>
+    <t>10.215.132.68</t>
+  </si>
+  <si>
+    <t>10.215.132.238</t>
+  </si>
+  <si>
+    <t>10.215.132.213</t>
+  </si>
+  <si>
+    <t>10.215.132.62</t>
+  </si>
+  <si>
+    <t>10.215.132.91</t>
+  </si>
+  <si>
+    <t>10.215.132.107</t>
+  </si>
+  <si>
+    <t>10.215.132.241</t>
+  </si>
+  <si>
+    <t>10.215.132.19</t>
+  </si>
+  <si>
+    <t>10.215.132.112</t>
+  </si>
+  <si>
+    <t>10.215.132.229</t>
+  </si>
+  <si>
+    <t>10.215.132.11</t>
+  </si>
+  <si>
+    <t>10.210.49.195</t>
+  </si>
+  <si>
+    <t>10.215.132.248</t>
+  </si>
+  <si>
+    <t>10.215.132.245</t>
+  </si>
+  <si>
+    <t>10.215.132.246</t>
+  </si>
+  <si>
+    <t>10.215.132.162</t>
+  </si>
+  <si>
+    <t>10.215.132.249</t>
+  </si>
+  <si>
+    <t>10.215.132.250</t>
+  </si>
+  <si>
+    <t>10.215.132.159</t>
+  </si>
+  <si>
+    <t>10.215.132.222</t>
+  </si>
+  <si>
+    <t>10.215.132.221</t>
+  </si>
+  <si>
+    <t>10.210.49.6</t>
+  </si>
+  <si>
+    <t>10.215.132.105</t>
+  </si>
+  <si>
+    <t>10.215.132.220</t>
+  </si>
+  <si>
+    <t>10.215.132.18</t>
+  </si>
+  <si>
+    <t>10.215.132.158</t>
+  </si>
+  <si>
+    <t>10.210.49.51</t>
+  </si>
+  <si>
+    <t>10.215.132.175</t>
+  </si>
+  <si>
+    <t>10.210.49.55</t>
+  </si>
+  <si>
+    <t>10.210.49.40</t>
+  </si>
+  <si>
+    <t>10.210.49.44</t>
+  </si>
+  <si>
+    <t>10.210.49.49</t>
+  </si>
+  <si>
+    <t>10.210.49.43</t>
+  </si>
+  <si>
+    <t>10.210.49.50</t>
+  </si>
+  <si>
+    <t>10.210.49.67</t>
+  </si>
+  <si>
+    <t>10.210.49.41</t>
+  </si>
+  <si>
+    <t>10.210.49.52</t>
+  </si>
+  <si>
+    <t>10.210.49.56</t>
+  </si>
+  <si>
+    <t>10.210.49.47</t>
+  </si>
+  <si>
+    <t>10.210.49.42</t>
+  </si>
+  <si>
+    <t>10.215.132.179</t>
+  </si>
+  <si>
+    <t>10.210.49.57</t>
+  </si>
+  <si>
+    <t>10.210.49.58</t>
+  </si>
+  <si>
+    <t>10.210.49.48</t>
+  </si>
+  <si>
+    <t>10.210.49.151</t>
+  </si>
+  <si>
+    <t>10.210.49.33</t>
+  </si>
+  <si>
+    <t>10.254.48.3</t>
+  </si>
+  <si>
+    <t>10.210.49.71</t>
+  </si>
+  <si>
+    <t>10.210.49.63</t>
+  </si>
+  <si>
+    <t>10.210.49.64</t>
+  </si>
+  <si>
+    <t>10.215.132.59</t>
+  </si>
+  <si>
+    <t>10.210.49.72</t>
+  </si>
+  <si>
+    <t>10.210.49.75</t>
+  </si>
+  <si>
+    <t>10.210.49.180</t>
+  </si>
+  <si>
+    <t>10.210.49.199</t>
+  </si>
+  <si>
+    <t>10.210.49.81</t>
+  </si>
+  <si>
+    <t>10.215.132.235</t>
+  </si>
+  <si>
+    <t>10.210.49.85</t>
+  </si>
+  <si>
+    <t>MAHESHWARAPU RANJITH KUMAR-KZP</t>
+  </si>
+  <si>
+    <t>10.210.49.198</t>
+  </si>
+  <si>
+    <t>10.210.49.157</t>
+  </si>
+  <si>
+    <t>10.210.49.156</t>
+  </si>
+  <si>
+    <t>10.210.49.73</t>
+  </si>
+  <si>
+    <t>10.215.132.181</t>
+  </si>
+  <si>
+    <t>10.215.132.231</t>
+  </si>
+  <si>
+    <t>10.210.49.158</t>
+  </si>
+  <si>
+    <t>10.210.49.80</t>
+  </si>
+  <si>
+    <t>10.210.49.61</t>
+  </si>
+  <si>
+    <t>10.210.49.205</t>
+  </si>
+  <si>
+    <t>SURENDER GUGULOTH</t>
+  </si>
+  <si>
+    <t>10.210.49.78</t>
+  </si>
+  <si>
+    <t>10.210.49.197</t>
+  </si>
+  <si>
+    <t>10.210.49.83</t>
+  </si>
+  <si>
+    <t>10.210.49.84</t>
+  </si>
+  <si>
+    <t>10.210.49.77</t>
+  </si>
+  <si>
+    <t>10.210.49.79</t>
+  </si>
+  <si>
+    <t>10.210.49.66</t>
+  </si>
+  <si>
+    <t>10.210.49.16</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,100 +855,52 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +938,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -211,6 +972,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -245,9 +1007,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -420,27 +1183,2023 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B251"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>OLT IP</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>BBC Name</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/OLT_BBC_MAP.xlsx
+++ b/OLT_BBC_MAP.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamsh\AppData\Local\Temp\MicrosoftEdgeDownloads\cfa36706-d488-40ce-b4bc-e85430139ad7\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C904E3-24EF-456B-9B61-8D9086EEFA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="267">
   <si>
     <t>OLT IP</t>
   </si>
@@ -49,9 +43,6 @@
     <t>10.215.132.177</t>
   </si>
   <si>
-    <t>A PRAVEEN-JAN</t>
-  </si>
-  <si>
     <t>10.215.132.163</t>
   </si>
   <si>
@@ -205,9 +196,6 @@
     <t>10.210.49.190</t>
   </si>
   <si>
-    <t>BHIKSHAPATHI MANCHALA</t>
-  </si>
-  <si>
     <t>10.215.132.132</t>
   </si>
   <si>
@@ -349,9 +337,6 @@
     <t>10.215.132.128</t>
   </si>
   <si>
-    <t>A PRAVEEN-CHR</t>
-  </si>
-  <si>
     <t>10.215.132.16</t>
   </si>
   <si>
@@ -809,13 +794,34 @@
   </si>
   <si>
     <t>10.210.49.16</t>
+  </si>
+  <si>
+    <t>MOHAMMAD SHAFEEQ</t>
+  </si>
+  <si>
+    <t>KIRAN NATTE</t>
+  </si>
+  <si>
+    <t>10.211.237.16</t>
+  </si>
+  <si>
+    <t>10.214.132.5</t>
+  </si>
+  <si>
+    <t>10.215.132.108</t>
+  </si>
+  <si>
+    <t>10.210.49.206</t>
+  </si>
+  <si>
+    <t>10.215.132.234</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,9 +904,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -938,7 +944,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -972,7 +978,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1007,10 +1012,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1183,15 +1187,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B251"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B256"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1199,351 +1203,351 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="3" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>246</v>
-      </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
         <v>7</v>
       </c>
@@ -1551,175 +1555,175 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="B55" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="3" t="s">
         <v>5</v>
       </c>
@@ -1727,367 +1731,367 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B73" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3" t="s">
+      <c r="B78" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="B88" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
       <c r="A102" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
+      <c r="B105" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="B107" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2">
       <c r="A111" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
       <c r="A112" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2">
       <c r="A113" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,1108 +2099,1148 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2">
       <c r="A114" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2">
       <c r="A115" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2">
       <c r="A116" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
       <c r="A117" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
       <c r="A118" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2">
       <c r="A119" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2">
       <c r="A120" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2">
       <c r="A121" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2">
       <c r="A122" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2">
       <c r="A123" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2">
       <c r="A124" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
       <c r="A125" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
       <c r="A126" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2">
       <c r="A127" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
       <c r="A128" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
       <c r="A129" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
       <c r="A130" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2">
       <c r="A131" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
       <c r="A132" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
       <c r="A133" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="B135" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
       <c r="A136" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
       <c r="A137" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2">
       <c r="A138" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
       <c r="A139" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
       <c r="A140" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2">
       <c r="A141" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2">
       <c r="A142" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
       <c r="A143" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
       <c r="A144" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
       <c r="A145" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
       <c r="A146" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A147" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="B154" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
       <c r="A155" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2">
       <c r="A156" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
       <c r="A157" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
       <c r="A158" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
       <c r="A159" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
       <c r="A160" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2">
       <c r="A161" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
       <c r="A162" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
       <c r="A163" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2">
       <c r="A164" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2">
       <c r="A165" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B165" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="B170" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
       <c r="A171" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
       <c r="A172" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
       <c r="A173" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2">
       <c r="A174" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
       <c r="A175" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
       <c r="A176" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
       <c r="A177" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2">
       <c r="A178" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
       <c r="A179" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
       <c r="A180" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2">
       <c r="A181" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
       <c r="A182" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2">
       <c r="A183" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
       <c r="A184" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
       <c r="A185" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
       <c r="A186" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
       <c r="A187" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
       <c r="A188" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
       <c r="A189" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2">
       <c r="A190" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2">
       <c r="A192" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2">
       <c r="A193" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
       <c r="A194" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="B195" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
       <c r="A196" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B197" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="B202" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
       <c r="A203" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
       <c r="A204" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
       <c r="A205" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
       <c r="A206" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
       <c r="A207" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
       <c r="A208" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
       <c r="A209" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2">
       <c r="A210" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
       <c r="A211" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
       <c r="A212" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
       <c r="A213" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B213" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A214" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="B215" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
       <c r="A216" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2">
       <c r="A217" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2">
       <c r="A218" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2">
       <c r="A219" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2">
       <c r="A220" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A221" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A222" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="B222" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
       <c r="A223" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
       <c r="A224" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A225" s="3" t="s">
+      <c r="B234" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A226" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A227" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A228" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A229" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A230" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A231" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A232" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A233" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A234" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A235" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B235" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A236" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A237" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A238" s="2" t="s">
+      <c r="B238" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A239" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A240" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A241" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="B241" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
       <c r="A242" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2">
       <c r="A243" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
       <c r="A244" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2">
       <c r="A245" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2">
       <c r="A246" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2">
       <c r="A247" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2">
       <c r="A248" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2">
       <c r="A249" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
       <c r="A250" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
       <c r="A251" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>32</v>
+      <c r="B252" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/OLT_BBC_MAP.xlsx
+++ b/OLT_BBC_MAP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="268">
   <si>
     <t>OLT IP</t>
   </si>
@@ -815,6 +815,9 @@
   </si>
   <si>
     <t>10.215.132.234</t>
+  </si>
+  <si>
+    <t>10.2100.49.153</t>
   </si>
 </sst>
 </file>
@@ -838,7 +841,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -848,6 +851,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -879,13 +894,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1188,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -3243,6 +3260,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/OLT_BBC_MAP.xlsx
+++ b/OLT_BBC_MAP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="271">
   <si>
     <t>OLT IP</t>
   </si>
@@ -818,6 +818,15 @@
   </si>
   <si>
     <t>10.2100.49.153</t>
+  </si>
+  <si>
+    <t>10.215.132.244</t>
+  </si>
+  <si>
+    <t>10.215.132.214</t>
+  </si>
+  <si>
+    <t>10.215.132.73</t>
   </si>
 </sst>
 </file>
@@ -894,7 +903,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -903,6 +912,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1205,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -3268,7 +3278,32 @@
         <v>261</v>
       </c>
     </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/OLT_BBC_MAP.xlsx
+++ b/OLT_BBC_MAP.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamsh\AppData\Local\Temp\MicrosoftEdgeDownloads\5fa08061-96ba-4fbc-8625-24e50b6d3267\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A5F74B-435F-44A9-AAA2-08CC60A1F199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -817,9 +823,6 @@
     <t>10.215.132.234</t>
   </si>
   <si>
-    <t>10.2100.49.153</t>
-  </si>
-  <si>
     <t>10.215.132.244</t>
   </si>
   <si>
@@ -827,13 +830,16 @@
   </si>
   <si>
     <t>10.215.132.73</t>
+  </si>
+  <si>
+    <t>10.210.49.153</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -903,7 +909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -912,7 +918,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -931,9 +936,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -971,7 +976,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1005,6 +1010,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1039,9 +1045,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1214,15 +1221,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B260"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1230,7 +1237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1238,7 +1245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1246,7 +1253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
@@ -1254,7 +1261,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>235</v>
       </c>
@@ -1262,7 +1269,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>230</v>
       </c>
@@ -1270,7 +1277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>246</v>
       </c>
@@ -1278,7 +1285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>226</v>
       </c>
@@ -1286,7 +1293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -1294,7 +1301,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1302,7 +1309,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>243</v>
       </c>
@@ -1310,7 +1317,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>149</v>
       </c>
@@ -1318,7 +1325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>247</v>
       </c>
@@ -1326,7 +1333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>89</v>
       </c>
@@ -1334,7 +1341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
@@ -1342,7 +1349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>86</v>
       </c>
@@ -1350,7 +1357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>88</v>
       </c>
@@ -1358,7 +1365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
@@ -1366,7 +1373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>87</v>
       </c>
@@ -1374,7 +1381,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>248</v>
       </c>
@@ -1382,7 +1389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>249</v>
       </c>
@@ -1390,7 +1397,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
@@ -1398,7 +1405,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>90</v>
       </c>
@@ -1406,7 +1413,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>105</v>
       </c>
@@ -1414,7 +1421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -1422,7 +1429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>103</v>
       </c>
@@ -1430,7 +1437,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>107</v>
       </c>
@@ -1438,7 +1445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>207</v>
       </c>
@@ -1446,7 +1453,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>206</v>
       </c>
@@ -1454,7 +1461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>43</v>
       </c>
@@ -1462,7 +1469,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>203</v>
       </c>
@@ -1470,7 +1477,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>121</v>
       </c>
@@ -1478,7 +1485,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>110</v>
       </c>
@@ -1486,7 +1493,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>60</v>
       </c>
@@ -1494,7 +1501,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>59</v>
       </c>
@@ -1502,7 +1509,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>101</v>
       </c>
@@ -1510,7 +1517,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>82</v>
       </c>
@@ -1518,7 +1525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>81</v>
       </c>
@@ -1526,7 +1533,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>193</v>
       </c>
@@ -1534,7 +1541,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>194</v>
       </c>
@@ -1542,7 +1549,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>15</v>
       </c>
@@ -1550,7 +1557,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>122</v>
       </c>
@@ -1558,7 +1565,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>96</v>
       </c>
@@ -1566,7 +1573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>190</v>
       </c>
@@ -1574,7 +1581,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>7</v>
       </c>
@@ -1582,7 +1589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>150</v>
       </c>
@@ -1590,7 +1597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>109</v>
       </c>
@@ -1598,7 +1605,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
@@ -1606,7 +1613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>16</v>
       </c>
@@ -1614,7 +1621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -1622,7 +1629,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>144</v>
       </c>
@@ -1630,7 +1637,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>94</v>
       </c>
@@ -1638,7 +1645,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>99</v>
       </c>
@@ -1646,7 +1653,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>8</v>
       </c>
@@ -1654,7 +1661,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>9</v>
       </c>
@@ -1662,7 +1669,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>102</v>
       </c>
@@ -1670,7 +1677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>51</v>
       </c>
@@ -1678,7 +1685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>95</v>
       </c>
@@ -1686,7 +1693,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>238</v>
       </c>
@@ -1694,7 +1701,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>143</v>
       </c>
@@ -1702,7 +1709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
@@ -1710,7 +1717,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>53</v>
       </c>
@@ -1718,7 +1725,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>52</v>
       </c>
@@ -1726,7 +1733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>242</v>
       </c>
@@ -1734,7 +1741,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>93</v>
       </c>
@@ -1742,7 +1749,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
@@ -1750,7 +1757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>5</v>
       </c>
@@ -1758,7 +1765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>10</v>
       </c>
@@ -1766,7 +1773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>78</v>
       </c>
@@ -1774,7 +1781,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>74</v>
       </c>
@@ -1782,7 +1789,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>73</v>
       </c>
@@ -1790,7 +1797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>62</v>
       </c>
@@ -1798,7 +1805,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>76</v>
       </c>
@@ -1806,7 +1813,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>70</v>
       </c>
@@ -1814,7 +1821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>63</v>
       </c>
@@ -1822,7 +1829,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>77</v>
       </c>
@@ -1830,7 +1837,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>79</v>
       </c>
@@ -1838,7 +1845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -1846,7 +1853,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>71</v>
       </c>
@@ -1854,7 +1861,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>252</v>
       </c>
@@ -1862,7 +1869,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>64</v>
       </c>
@@ -1870,7 +1877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>75</v>
       </c>
@@ -1878,7 +1885,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>66</v>
       </c>
@@ -1886,7 +1893,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>68</v>
       </c>
@@ -1894,7 +1901,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>65</v>
       </c>
@@ -1902,7 +1909,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>67</v>
       </c>
@@ -1910,7 +1917,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>69</v>
       </c>
@@ -1918,7 +1925,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>72</v>
       </c>
@@ -1926,7 +1933,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>188</v>
       </c>
@@ -1934,7 +1941,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>189</v>
       </c>
@@ -1942,7 +1949,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>106</v>
       </c>
@@ -1950,7 +1957,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>115</v>
       </c>
@@ -1958,7 +1965,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>13</v>
       </c>
@@ -1966,7 +1973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>205</v>
       </c>
@@ -1974,7 +1981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>204</v>
       </c>
@@ -1982,7 +1989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>49</v>
       </c>
@@ -1990,7 +1997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>48</v>
       </c>
@@ -1998,7 +2005,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>141</v>
       </c>
@@ -2006,7 +2013,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>140</v>
       </c>
@@ -2014,7 +2021,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>139</v>
       </c>
@@ -2022,7 +2029,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>138</v>
       </c>
@@ -2030,7 +2037,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>233</v>
       </c>
@@ -2038,7 +2045,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>58</v>
       </c>
@@ -2046,7 +2053,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>55</v>
       </c>
@@ -2054,7 +2061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>56</v>
       </c>
@@ -2062,7 +2069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>54</v>
       </c>
@@ -2070,7 +2077,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>57</v>
       </c>
@@ -2078,7 +2085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>104</v>
       </c>
@@ -2086,7 +2093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>91</v>
       </c>
@@ -2094,7 +2101,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>19</v>
       </c>
@@ -2102,7 +2109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>119</v>
       </c>
@@ -2110,7 +2117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>98</v>
       </c>
@@ -2118,7 +2125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>3</v>
       </c>
@@ -2126,7 +2133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>97</v>
       </c>
@@ -2134,7 +2141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>123</v>
       </c>
@@ -2142,7 +2149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>148</v>
       </c>
@@ -2150,7 +2157,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>137</v>
       </c>
@@ -2158,7 +2165,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>199</v>
       </c>
@@ -2166,7 +2173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>200</v>
       </c>
@@ -2174,7 +2181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>198</v>
       </c>
@@ -2182,7 +2189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>196</v>
       </c>
@@ -2190,7 +2197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>197</v>
       </c>
@@ -2198,7 +2205,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>195</v>
       </c>
@@ -2206,7 +2213,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>191</v>
       </c>
@@ -2214,7 +2221,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>192</v>
       </c>
@@ -2222,7 +2229,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>114</v>
       </c>
@@ -2230,7 +2237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>47</v>
       </c>
@@ -2238,7 +2245,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>146</v>
       </c>
@@ -2246,7 +2253,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>136</v>
       </c>
@@ -2254,7 +2261,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>147</v>
       </c>
@@ -2262,7 +2269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>120</v>
       </c>
@@ -2270,7 +2277,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>33</v>
       </c>
@@ -2278,7 +2285,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>142</v>
       </c>
@@ -2286,7 +2293,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>17</v>
       </c>
@@ -2294,7 +2301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>145</v>
       </c>
@@ -2302,7 +2309,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>201</v>
       </c>
@@ -2310,7 +2317,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>124</v>
       </c>
@@ -2318,7 +2325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>14</v>
       </c>
@@ -2326,7 +2333,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>202</v>
       </c>
@@ -2334,7 +2341,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>36</v>
       </c>
@@ -2342,7 +2349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>37</v>
       </c>
@@ -2350,7 +2357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>118</v>
       </c>
@@ -2358,7 +2365,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>117</v>
       </c>
@@ -2366,7 +2373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>181</v>
       </c>
@@ -2374,7 +2381,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>155</v>
       </c>
@@ -2382,7 +2389,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>172</v>
       </c>
@@ -2390,7 +2397,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>179</v>
       </c>
@@ -2398,7 +2405,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>185</v>
       </c>
@@ -2406,7 +2413,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>171</v>
       </c>
@@ -2414,7 +2421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>163</v>
       </c>
@@ -2422,7 +2429,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>180</v>
       </c>
@@ -2430,7 +2437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>170</v>
       </c>
@@ -2438,7 +2445,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>153</v>
       </c>
@@ -2446,7 +2453,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>175</v>
       </c>
@@ -2454,7 +2461,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>169</v>
       </c>
@@ -2462,7 +2469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>159</v>
       </c>
@@ -2470,7 +2477,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>176</v>
       </c>
@@ -2478,7 +2485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>157</v>
       </c>
@@ -2486,7 +2493,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>168</v>
       </c>
@@ -2494,7 +2501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>154</v>
       </c>
@@ -2502,7 +2509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>152</v>
       </c>
@@ -2510,7 +2517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>161</v>
       </c>
@@ -2518,7 +2525,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>167</v>
       </c>
@@ -2526,7 +2533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>186</v>
       </c>
@@ -2534,7 +2541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>162</v>
       </c>
@@ -2542,7 +2549,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>166</v>
       </c>
@@ -2550,7 +2557,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>160</v>
       </c>
@@ -2558,7 +2565,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>184</v>
       </c>
@@ -2566,7 +2573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>173</v>
       </c>
@@ -2574,7 +2581,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>165</v>
       </c>
@@ -2582,7 +2589,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>183</v>
       </c>
@@ -2590,7 +2597,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>178</v>
       </c>
@@ -2598,7 +2605,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>177</v>
       </c>
@@ -2606,7 +2613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>164</v>
       </c>
@@ -2614,7 +2621,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>158</v>
       </c>
@@ -2622,7 +2629,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>156</v>
       </c>
@@ -2630,7 +2637,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>187</v>
       </c>
@@ -2638,7 +2645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>182</v>
       </c>
@@ -2646,7 +2653,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>174</v>
       </c>
@@ -2654,7 +2661,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>151</v>
       </c>
@@ -2662,7 +2669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>253</v>
       </c>
@@ -2670,7 +2677,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>113</v>
       </c>
@@ -2678,7 +2685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>29</v>
       </c>
@@ -2686,7 +2693,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>239</v>
       </c>
@@ -2694,7 +2701,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>254</v>
       </c>
@@ -2702,7 +2709,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>236</v>
       </c>
@@ -2710,7 +2717,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>35</v>
       </c>
@@ -2718,7 +2725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>34</v>
       </c>
@@ -2726,7 +2733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>255</v>
       </c>
@@ -2734,7 +2741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>116</v>
       </c>
@@ -2742,7 +2749,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>44</v>
       </c>
@@ -2750,7 +2757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>45</v>
       </c>
@@ -2758,7 +2765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>134</v>
       </c>
@@ -2766,7 +2773,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>130</v>
       </c>
@@ -2774,7 +2781,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>133</v>
       </c>
@@ -2782,7 +2789,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>126</v>
       </c>
@@ -2790,7 +2797,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>127</v>
       </c>
@@ -2798,7 +2805,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>128</v>
       </c>
@@ -2806,7 +2813,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>132</v>
       </c>
@@ -2814,7 +2821,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>125</v>
       </c>
@@ -2822,7 +2829,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>131</v>
       </c>
@@ -2830,7 +2837,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>129</v>
       </c>
@@ -2838,7 +2845,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>232</v>
       </c>
@@ -2846,7 +2853,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>23</v>
       </c>
@@ -2854,7 +2861,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>108</v>
       </c>
@@ -2862,7 +2869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>112</v>
       </c>
@@ -2870,7 +2877,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>244</v>
       </c>
@@ -2878,7 +2885,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>256</v>
       </c>
@@ -2886,7 +2893,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>42</v>
       </c>
@@ -2894,7 +2901,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>32</v>
       </c>
@@ -2902,7 +2909,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>229</v>
       </c>
@@ -2910,7 +2917,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>92</v>
       </c>
@@ -2918,7 +2925,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>231</v>
       </c>
@@ -2926,7 +2933,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>227</v>
       </c>
@@ -2934,7 +2941,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>234</v>
       </c>
@@ -2942,7 +2949,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>257</v>
       </c>
@@ -2950,7 +2957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>100</v>
       </c>
@@ -2958,7 +2965,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>241</v>
       </c>
@@ -2966,7 +2973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>111</v>
       </c>
@@ -2974,7 +2981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>27</v>
       </c>
@@ -2982,7 +2989,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>26</v>
       </c>
@@ -2990,7 +2997,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>28</v>
       </c>
@@ -2998,7 +3005,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>46</v>
       </c>
@@ -3006,7 +3013,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>221</v>
       </c>
@@ -3014,7 +3021,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>216</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>218</v>
       </c>
@@ -3030,7 +3037,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>215</v>
       </c>
@@ -3038,7 +3045,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>208</v>
       </c>
@@ -3046,7 +3053,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>220</v>
       </c>
@@ -3054,7 +3061,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>213</v>
       </c>
@@ -3062,7 +3069,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>212</v>
       </c>
@@ -3070,7 +3077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>210</v>
       </c>
@@ -3078,7 +3085,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>217</v>
       </c>
@@ -3086,7 +3093,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>224</v>
       </c>
@@ -3094,7 +3101,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>211</v>
       </c>
@@ -3102,7 +3109,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>223</v>
       </c>
@@ -3110,7 +3117,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>214</v>
       </c>
@@ -3118,7 +3125,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>219</v>
       </c>
@@ -3126,7 +3133,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>225</v>
       </c>
@@ -3134,7 +3141,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>209</v>
       </c>
@@ -3142,7 +3149,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>222</v>
       </c>
@@ -3150,7 +3157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>258</v>
       </c>
@@ -3158,7 +3165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>237</v>
       </c>
@@ -3166,7 +3173,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>135</v>
       </c>
@@ -3174,7 +3181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>39</v>
       </c>
@@ -3182,7 +3189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>40</v>
       </c>
@@ -3190,7 +3197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>245</v>
       </c>
@@ -3198,7 +3205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>41</v>
       </c>
@@ -3206,7 +3213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>22</v>
       </c>
@@ -3214,7 +3221,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>228</v>
       </c>
@@ -3222,7 +3229,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>259</v>
       </c>
@@ -3230,7 +3237,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>262</v>
       </c>
@@ -3238,7 +3245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>263</v>
       </c>
@@ -3246,7 +3253,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>264</v>
       </c>
@@ -3254,7 +3261,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>265</v>
       </c>
@@ -3262,7 +3269,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>266</v>
       </c>
@@ -3270,33 +3277,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2">
-      <c r="A258" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
-      <c r="A259" s="6" t="s">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="B259" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2">
-      <c r="A260" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>251</v>

--- a/OLT_BBC_MAP.xlsx
+++ b/OLT_BBC_MAP.xlsx
@@ -1,26 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamsh\AppData\Local\Temp\MicrosoftEdgeDownloads\5fa08061-96ba-4fbc-8625-24e50b6d3267\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A5F74B-435F-44A9-AAA2-08CC60A1F199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$260</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="273">
   <si>
     <t>OLT IP</t>
   </si>
@@ -833,13 +830,19 @@
   </si>
   <si>
     <t>10.210.49.153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.210.49.153 </t>
+  </si>
+  <si>
+    <t>10.210.49.207</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -882,7 +885,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -905,11 +908,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -918,6 +932,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -936,9 +952,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -976,7 +992,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1010,7 +1026,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1045,10 +1060,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1221,15 +1235,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B260"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B263"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1237,7 +1251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1245,7 +1259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1253,7 +1267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>83</v>
       </c>
@@ -1261,7 +1275,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>235</v>
       </c>
@@ -1269,7 +1283,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>230</v>
       </c>
@@ -1277,7 +1291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
         <v>246</v>
       </c>
@@ -1285,7 +1299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>226</v>
       </c>
@@ -1293,7 +1307,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -1301,7 +1315,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1309,7 +1323,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
         <v>243</v>
       </c>
@@ -1317,7 +1331,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
         <v>149</v>
       </c>
@@ -1325,7 +1339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
         <v>247</v>
       </c>
@@ -1333,7 +1347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
         <v>89</v>
       </c>
@@ -1341,7 +1355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
@@ -1349,7 +1363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
         <v>86</v>
       </c>
@@ -1357,7 +1371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>88</v>
       </c>
@@ -1365,7 +1379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" s="2" t="s">
         <v>84</v>
       </c>
@@ -1373,7 +1387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
         <v>87</v>
       </c>
@@ -1381,7 +1395,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
         <v>248</v>
       </c>
@@ -1389,7 +1403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
         <v>249</v>
       </c>
@@ -1397,7 +1411,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
@@ -1405,7 +1419,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
         <v>90</v>
       </c>
@@ -1413,7 +1427,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
         <v>105</v>
       </c>
@@ -1421,7 +1435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
         <v>250</v>
       </c>
@@ -1429,7 +1443,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>103</v>
       </c>
@@ -1437,7 +1451,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" s="3" t="s">
         <v>107</v>
       </c>
@@ -1445,7 +1459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" s="2" t="s">
         <v>207</v>
       </c>
@@ -1453,7 +1467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" s="3" t="s">
         <v>206</v>
       </c>
@@ -1461,7 +1475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
         <v>43</v>
       </c>
@@ -1469,7 +1483,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" s="3" t="s">
         <v>203</v>
       </c>
@@ -1477,7 +1491,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2">
       <c r="A32" s="2" t="s">
         <v>121</v>
       </c>
@@ -1485,7 +1499,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" s="3" t="s">
         <v>110</v>
       </c>
@@ -1493,7 +1507,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" s="2" t="s">
         <v>60</v>
       </c>
@@ -1501,7 +1515,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
         <v>59</v>
       </c>
@@ -1509,7 +1523,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
         <v>101</v>
       </c>
@@ -1517,7 +1531,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" s="3" t="s">
         <v>82</v>
       </c>
@@ -1525,7 +1539,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" s="2" t="s">
         <v>81</v>
       </c>
@@ -1533,7 +1547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
         <v>193</v>
       </c>
@@ -1541,7 +1555,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" s="2" t="s">
         <v>194</v>
       </c>
@@ -1549,7 +1563,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
         <v>15</v>
       </c>
@@ -1557,7 +1571,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" s="2" t="s">
         <v>122</v>
       </c>
@@ -1565,7 +1579,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
         <v>96</v>
       </c>
@@ -1573,7 +1587,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" s="2" t="s">
         <v>190</v>
       </c>
@@ -1581,7 +1595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
         <v>7</v>
       </c>
@@ -1589,7 +1603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" s="2" t="s">
         <v>150</v>
       </c>
@@ -1597,7 +1611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" s="3" t="s">
         <v>109</v>
       </c>
@@ -1605,7 +1619,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
@@ -1613,7 +1627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
         <v>16</v>
       </c>
@@ -1621,7 +1635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -1629,7 +1643,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" s="3" t="s">
         <v>144</v>
       </c>
@@ -1637,7 +1651,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" s="2" t="s">
         <v>94</v>
       </c>
@@ -1645,7 +1659,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" s="3" t="s">
         <v>99</v>
       </c>
@@ -1653,7 +1667,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" s="2" t="s">
         <v>8</v>
       </c>
@@ -1661,7 +1675,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" s="3" t="s">
         <v>9</v>
       </c>
@@ -1669,7 +1683,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" s="2" t="s">
         <v>102</v>
       </c>
@@ -1677,7 +1691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2">
       <c r="A57" s="3" t="s">
         <v>51</v>
       </c>
@@ -1685,7 +1699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2">
       <c r="A58" s="2" t="s">
         <v>95</v>
       </c>
@@ -1693,7 +1707,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2">
       <c r="A59" s="3" t="s">
         <v>238</v>
       </c>
@@ -1701,7 +1715,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" s="2" t="s">
         <v>143</v>
       </c>
@@ -1709,7 +1723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
@@ -1717,7 +1731,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" s="2" t="s">
         <v>53</v>
       </c>
@@ -1725,7 +1739,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" s="3" t="s">
         <v>52</v>
       </c>
@@ -1733,7 +1747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" s="2" t="s">
         <v>242</v>
       </c>
@@ -1741,7 +1755,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" s="3" t="s">
         <v>93</v>
       </c>
@@ -1749,7 +1763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
@@ -1757,7 +1771,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" s="3" t="s">
         <v>5</v>
       </c>
@@ -1765,7 +1779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" s="2" t="s">
         <v>10</v>
       </c>
@@ -1773,7 +1787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" s="3" t="s">
         <v>78</v>
       </c>
@@ -1781,7 +1795,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" s="2" t="s">
         <v>74</v>
       </c>
@@ -1789,7 +1803,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" s="3" t="s">
         <v>73</v>
       </c>
@@ -1797,7 +1811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2">
       <c r="A72" s="2" t="s">
         <v>62</v>
       </c>
@@ -1805,7 +1819,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" s="3" t="s">
         <v>76</v>
       </c>
@@ -1813,7 +1827,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2">
       <c r="A74" s="2" t="s">
         <v>70</v>
       </c>
@@ -1821,7 +1835,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" s="3" t="s">
         <v>63</v>
       </c>
@@ -1829,7 +1843,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2">
       <c r="A76" s="2" t="s">
         <v>77</v>
       </c>
@@ -1837,7 +1851,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" s="3" t="s">
         <v>79</v>
       </c>
@@ -1845,7 +1859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -1853,7 +1867,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2">
       <c r="A79" s="3" t="s">
         <v>71</v>
       </c>
@@ -1861,7 +1875,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" s="2" t="s">
         <v>252</v>
       </c>
@@ -1869,7 +1883,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2">
       <c r="A81" s="3" t="s">
         <v>64</v>
       </c>
@@ -1877,7 +1891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2">
       <c r="A82" s="2" t="s">
         <v>75</v>
       </c>
@@ -1885,7 +1899,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" s="3" t="s">
         <v>66</v>
       </c>
@@ -1893,7 +1907,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" s="2" t="s">
         <v>68</v>
       </c>
@@ -1901,7 +1915,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" s="3" t="s">
         <v>65</v>
       </c>
@@ -1909,7 +1923,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" s="2" t="s">
         <v>67</v>
       </c>
@@ -1917,7 +1931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2">
       <c r="A87" s="3" t="s">
         <v>69</v>
       </c>
@@ -1925,7 +1939,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2">
       <c r="A88" s="2" t="s">
         <v>72</v>
       </c>
@@ -1933,7 +1947,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2">
       <c r="A89" s="3" t="s">
         <v>188</v>
       </c>
@@ -1941,7 +1955,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2">
       <c r="A90" s="2" t="s">
         <v>189</v>
       </c>
@@ -1949,7 +1963,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2">
       <c r="A91" s="3" t="s">
         <v>106</v>
       </c>
@@ -1957,7 +1971,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2">
       <c r="A92" s="2" t="s">
         <v>115</v>
       </c>
@@ -1965,7 +1979,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2">
       <c r="A93" s="3" t="s">
         <v>13</v>
       </c>
@@ -1973,7 +1987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" s="2" t="s">
         <v>205</v>
       </c>
@@ -1981,7 +1995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" s="3" t="s">
         <v>204</v>
       </c>
@@ -1989,7 +2003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" s="2" t="s">
         <v>49</v>
       </c>
@@ -1997,7 +2011,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2">
       <c r="A97" s="3" t="s">
         <v>48</v>
       </c>
@@ -2005,7 +2019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2">
       <c r="A98" s="2" t="s">
         <v>141</v>
       </c>
@@ -2013,7 +2027,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2">
       <c r="A99" s="3" t="s">
         <v>140</v>
       </c>
@@ -2021,7 +2035,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2">
       <c r="A100" s="2" t="s">
         <v>139</v>
       </c>
@@ -2029,7 +2043,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2">
       <c r="A101" s="3" t="s">
         <v>138</v>
       </c>
@@ -2037,7 +2051,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2">
       <c r="A102" s="2" t="s">
         <v>233</v>
       </c>
@@ -2045,7 +2059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2">
       <c r="A103" s="3" t="s">
         <v>58</v>
       </c>
@@ -2053,7 +2067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2">
       <c r="A104" s="2" t="s">
         <v>55</v>
       </c>
@@ -2061,7 +2075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2">
       <c r="A105" s="3" t="s">
         <v>56</v>
       </c>
@@ -2069,7 +2083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2">
       <c r="A106" s="2" t="s">
         <v>54</v>
       </c>
@@ -2077,7 +2091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2">
       <c r="A107" s="3" t="s">
         <v>57</v>
       </c>
@@ -2085,7 +2099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2">
       <c r="A108" s="2" t="s">
         <v>104</v>
       </c>
@@ -2093,7 +2107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2">
       <c r="A109" s="3" t="s">
         <v>91</v>
       </c>
@@ -2101,7 +2115,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2">
       <c r="A110" s="2" t="s">
         <v>19</v>
       </c>
@@ -2109,7 +2123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2">
       <c r="A111" s="3" t="s">
         <v>119</v>
       </c>
@@ -2117,7 +2131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2">
       <c r="A112" s="2" t="s">
         <v>98</v>
       </c>
@@ -2125,7 +2139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2">
       <c r="A113" s="3" t="s">
         <v>3</v>
       </c>
@@ -2133,7 +2147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2">
       <c r="A114" s="2" t="s">
         <v>97</v>
       </c>
@@ -2141,7 +2155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2">
       <c r="A115" s="3" t="s">
         <v>123</v>
       </c>
@@ -2149,7 +2163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2">
       <c r="A116" s="2" t="s">
         <v>148</v>
       </c>
@@ -2157,7 +2171,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2">
       <c r="A117" s="3" t="s">
         <v>137</v>
       </c>
@@ -2165,7 +2179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2">
       <c r="A118" s="2" t="s">
         <v>199</v>
       </c>
@@ -2173,7 +2187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2">
       <c r="A119" s="3" t="s">
         <v>200</v>
       </c>
@@ -2181,7 +2195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2">
       <c r="A120" s="2" t="s">
         <v>198</v>
       </c>
@@ -2189,7 +2203,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2">
       <c r="A121" s="3" t="s">
         <v>196</v>
       </c>
@@ -2197,7 +2211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2">
       <c r="A122" s="2" t="s">
         <v>197</v>
       </c>
@@ -2205,7 +2219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2">
       <c r="A123" s="3" t="s">
         <v>195</v>
       </c>
@@ -2213,7 +2227,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2">
       <c r="A124" s="2" t="s">
         <v>191</v>
       </c>
@@ -2221,7 +2235,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2">
       <c r="A125" s="3" t="s">
         <v>192</v>
       </c>
@@ -2229,7 +2243,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2">
       <c r="A126" s="2" t="s">
         <v>114</v>
       </c>
@@ -2237,7 +2251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2">
       <c r="A127" s="3" t="s">
         <v>47</v>
       </c>
@@ -2245,7 +2259,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2">
       <c r="A128" s="2" t="s">
         <v>146</v>
       </c>
@@ -2253,7 +2267,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2">
       <c r="A129" s="3" t="s">
         <v>136</v>
       </c>
@@ -2261,7 +2275,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2">
       <c r="A130" s="2" t="s">
         <v>147</v>
       </c>
@@ -2269,7 +2283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2">
       <c r="A131" s="3" t="s">
         <v>120</v>
       </c>
@@ -2277,7 +2291,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2">
       <c r="A132" s="2" t="s">
         <v>33</v>
       </c>
@@ -2285,7 +2299,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2">
       <c r="A133" s="3" t="s">
         <v>142</v>
       </c>
@@ -2293,7 +2307,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2">
       <c r="A134" s="2" t="s">
         <v>17</v>
       </c>
@@ -2301,7 +2315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2">
       <c r="A135" s="3" t="s">
         <v>145</v>
       </c>
@@ -2309,7 +2323,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2">
       <c r="A136" s="2" t="s">
         <v>201</v>
       </c>
@@ -2317,7 +2331,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2">
       <c r="A137" s="3" t="s">
         <v>124</v>
       </c>
@@ -2325,7 +2339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2">
       <c r="A138" s="2" t="s">
         <v>14</v>
       </c>
@@ -2333,7 +2347,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2">
       <c r="A139" s="3" t="s">
         <v>202</v>
       </c>
@@ -2341,7 +2355,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2">
       <c r="A140" s="2" t="s">
         <v>36</v>
       </c>
@@ -2349,7 +2363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2">
       <c r="A141" s="3" t="s">
         <v>37</v>
       </c>
@@ -2357,7 +2371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2">
       <c r="A142" s="2" t="s">
         <v>118</v>
       </c>
@@ -2365,7 +2379,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2">
       <c r="A143" s="3" t="s">
         <v>117</v>
       </c>
@@ -2373,7 +2387,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2">
       <c r="A144" s="2" t="s">
         <v>181</v>
       </c>
@@ -2381,7 +2395,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2">
       <c r="A145" s="3" t="s">
         <v>155</v>
       </c>
@@ -2389,7 +2403,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2">
       <c r="A146" s="2" t="s">
         <v>172</v>
       </c>
@@ -2397,7 +2411,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2">
       <c r="A147" s="3" t="s">
         <v>179</v>
       </c>
@@ -2405,7 +2419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2">
       <c r="A148" s="2" t="s">
         <v>185</v>
       </c>
@@ -2413,7 +2427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2">
       <c r="A149" s="3" t="s">
         <v>171</v>
       </c>
@@ -2421,7 +2435,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2">
       <c r="A150" s="2" t="s">
         <v>163</v>
       </c>
@@ -2429,7 +2443,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2">
       <c r="A151" s="3" t="s">
         <v>180</v>
       </c>
@@ -2437,7 +2451,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2">
       <c r="A152" s="2" t="s">
         <v>170</v>
       </c>
@@ -2445,7 +2459,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2">
       <c r="A153" s="3" t="s">
         <v>153</v>
       </c>
@@ -2453,7 +2467,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2">
       <c r="A154" s="2" t="s">
         <v>175</v>
       </c>
@@ -2461,7 +2475,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2">
       <c r="A155" s="3" t="s">
         <v>169</v>
       </c>
@@ -2469,7 +2483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2">
       <c r="A156" s="2" t="s">
         <v>159</v>
       </c>
@@ -2477,7 +2491,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2">
       <c r="A157" s="3" t="s">
         <v>176</v>
       </c>
@@ -2485,7 +2499,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2">
       <c r="A158" s="2" t="s">
         <v>157</v>
       </c>
@@ -2493,7 +2507,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2">
       <c r="A159" s="3" t="s">
         <v>168</v>
       </c>
@@ -2501,7 +2515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2">
       <c r="A160" s="2" t="s">
         <v>154</v>
       </c>
@@ -2509,7 +2523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2">
       <c r="A161" s="3" t="s">
         <v>152</v>
       </c>
@@ -2517,7 +2531,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2">
       <c r="A162" s="2" t="s">
         <v>161</v>
       </c>
@@ -2525,7 +2539,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2">
       <c r="A163" s="3" t="s">
         <v>167</v>
       </c>
@@ -2533,7 +2547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2">
       <c r="A164" s="2" t="s">
         <v>186</v>
       </c>
@@ -2541,7 +2555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2">
       <c r="A165" s="3" t="s">
         <v>162</v>
       </c>
@@ -2549,7 +2563,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2">
       <c r="A166" s="2" t="s">
         <v>166</v>
       </c>
@@ -2557,7 +2571,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2">
       <c r="A167" s="3" t="s">
         <v>160</v>
       </c>
@@ -2565,7 +2579,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2">
       <c r="A168" s="2" t="s">
         <v>184</v>
       </c>
@@ -2573,7 +2587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2">
       <c r="A169" s="3" t="s">
         <v>173</v>
       </c>
@@ -2581,7 +2595,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2">
       <c r="A170" s="2" t="s">
         <v>165</v>
       </c>
@@ -2589,7 +2603,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2">
       <c r="A171" s="3" t="s">
         <v>183</v>
       </c>
@@ -2597,7 +2611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2">
       <c r="A172" s="2" t="s">
         <v>178</v>
       </c>
@@ -2605,7 +2619,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2">
       <c r="A173" s="3" t="s">
         <v>177</v>
       </c>
@@ -2613,7 +2627,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2">
       <c r="A174" s="2" t="s">
         <v>164</v>
       </c>
@@ -2621,7 +2635,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2">
       <c r="A175" s="3" t="s">
         <v>158</v>
       </c>
@@ -2629,7 +2643,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2">
       <c r="A176" s="2" t="s">
         <v>156</v>
       </c>
@@ -2637,7 +2651,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2">
       <c r="A177" s="3" t="s">
         <v>187</v>
       </c>
@@ -2645,7 +2659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2">
       <c r="A178" s="2" t="s">
         <v>182</v>
       </c>
@@ -2653,7 +2667,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2">
       <c r="A179" s="3" t="s">
         <v>174</v>
       </c>
@@ -2661,7 +2675,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2">
       <c r="A180" s="2" t="s">
         <v>151</v>
       </c>
@@ -2669,7 +2683,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2">
       <c r="A181" s="3" t="s">
         <v>253</v>
       </c>
@@ -2677,7 +2691,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2">
       <c r="A182" s="2" t="s">
         <v>113</v>
       </c>
@@ -2685,7 +2699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2">
       <c r="A183" s="3" t="s">
         <v>29</v>
       </c>
@@ -2693,7 +2707,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2">
       <c r="A184" s="2" t="s">
         <v>239</v>
       </c>
@@ -2701,7 +2715,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2">
       <c r="A185" s="3" t="s">
         <v>254</v>
       </c>
@@ -2709,7 +2723,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2">
       <c r="A186" s="2" t="s">
         <v>236</v>
       </c>
@@ -2717,7 +2731,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2">
       <c r="A187" s="3" t="s">
         <v>35</v>
       </c>
@@ -2725,7 +2739,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2">
       <c r="A188" s="2" t="s">
         <v>34</v>
       </c>
@@ -2733,7 +2747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2">
       <c r="A189" s="3" t="s">
         <v>255</v>
       </c>
@@ -2741,7 +2755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2">
       <c r="A190" s="2" t="s">
         <v>116</v>
       </c>
@@ -2749,7 +2763,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2">
       <c r="A191" s="3" t="s">
         <v>44</v>
       </c>
@@ -2757,7 +2771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2">
       <c r="A192" s="2" t="s">
         <v>45</v>
       </c>
@@ -2765,7 +2779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2">
       <c r="A193" s="3" t="s">
         <v>134</v>
       </c>
@@ -2773,7 +2787,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2">
       <c r="A194" s="2" t="s">
         <v>130</v>
       </c>
@@ -2781,7 +2795,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2">
       <c r="A195" s="3" t="s">
         <v>133</v>
       </c>
@@ -2789,7 +2803,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2">
       <c r="A196" s="2" t="s">
         <v>126</v>
       </c>
@@ -2797,7 +2811,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2">
       <c r="A197" s="3" t="s">
         <v>127</v>
       </c>
@@ -2805,7 +2819,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2">
       <c r="A198" s="2" t="s">
         <v>128</v>
       </c>
@@ -2813,7 +2827,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2">
       <c r="A199" s="3" t="s">
         <v>132</v>
       </c>
@@ -2821,7 +2835,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2">
       <c r="A200" s="2" t="s">
         <v>125</v>
       </c>
@@ -2829,7 +2843,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2">
       <c r="A201" s="3" t="s">
         <v>131</v>
       </c>
@@ -2837,7 +2851,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2">
       <c r="A202" s="2" t="s">
         <v>129</v>
       </c>
@@ -2845,7 +2859,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2">
       <c r="A203" s="3" t="s">
         <v>232</v>
       </c>
@@ -2853,7 +2867,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2">
       <c r="A204" s="2" t="s">
         <v>23</v>
       </c>
@@ -2861,7 +2875,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2">
       <c r="A205" s="3" t="s">
         <v>108</v>
       </c>
@@ -2869,7 +2883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2">
       <c r="A206" s="2" t="s">
         <v>112</v>
       </c>
@@ -2877,7 +2891,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2">
       <c r="A207" s="3" t="s">
         <v>244</v>
       </c>
@@ -2885,7 +2899,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2">
       <c r="A208" s="2" t="s">
         <v>256</v>
       </c>
@@ -2893,7 +2907,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2">
       <c r="A209" s="3" t="s">
         <v>42</v>
       </c>
@@ -2901,7 +2915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2">
       <c r="A210" s="2" t="s">
         <v>32</v>
       </c>
@@ -2909,7 +2923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2">
       <c r="A211" s="3" t="s">
         <v>229</v>
       </c>
@@ -2917,7 +2931,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2">
       <c r="A212" s="2" t="s">
         <v>92</v>
       </c>
@@ -2925,7 +2939,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2">
       <c r="A213" s="3" t="s">
         <v>231</v>
       </c>
@@ -2933,7 +2947,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2">
       <c r="A214" s="2" t="s">
         <v>227</v>
       </c>
@@ -2941,7 +2955,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2">
       <c r="A215" s="3" t="s">
         <v>234</v>
       </c>
@@ -2949,7 +2963,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2">
       <c r="A216" s="2" t="s">
         <v>257</v>
       </c>
@@ -2957,7 +2971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2">
       <c r="A217" s="3" t="s">
         <v>100</v>
       </c>
@@ -2965,7 +2979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2">
       <c r="A218" s="2" t="s">
         <v>241</v>
       </c>
@@ -2973,7 +2987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2">
       <c r="A219" s="3" t="s">
         <v>111</v>
       </c>
@@ -2981,7 +2995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2">
       <c r="A220" s="2" t="s">
         <v>27</v>
       </c>
@@ -2989,7 +3003,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2">
       <c r="A221" s="3" t="s">
         <v>26</v>
       </c>
@@ -2997,7 +3011,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2">
       <c r="A222" s="2" t="s">
         <v>28</v>
       </c>
@@ -3005,7 +3019,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2">
       <c r="A223" s="3" t="s">
         <v>46</v>
       </c>
@@ -3013,7 +3027,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2">
       <c r="A224" s="2" t="s">
         <v>221</v>
       </c>
@@ -3021,7 +3035,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2">
       <c r="A225" s="3" t="s">
         <v>216</v>
       </c>
@@ -3029,7 +3043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2">
       <c r="A226" s="2" t="s">
         <v>218</v>
       </c>
@@ -3037,7 +3051,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2">
       <c r="A227" s="3" t="s">
         <v>215</v>
       </c>
@@ -3045,7 +3059,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2">
       <c r="A228" s="2" t="s">
         <v>208</v>
       </c>
@@ -3053,7 +3067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2">
       <c r="A229" s="3" t="s">
         <v>220</v>
       </c>
@@ -3061,7 +3075,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2">
       <c r="A230" s="2" t="s">
         <v>213</v>
       </c>
@@ -3069,7 +3083,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2">
       <c r="A231" s="3" t="s">
         <v>212</v>
       </c>
@@ -3077,7 +3091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2">
       <c r="A232" s="2" t="s">
         <v>210</v>
       </c>
@@ -3085,7 +3099,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2">
       <c r="A233" s="3" t="s">
         <v>217</v>
       </c>
@@ -3093,7 +3107,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2">
       <c r="A234" s="2" t="s">
         <v>224</v>
       </c>
@@ -3101,7 +3115,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2">
       <c r="A235" s="3" t="s">
         <v>211</v>
       </c>
@@ -3109,7 +3123,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2">
       <c r="A236" s="2" t="s">
         <v>223</v>
       </c>
@@ -3117,7 +3131,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2">
       <c r="A237" s="3" t="s">
         <v>214</v>
       </c>
@@ -3125,7 +3139,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2">
       <c r="A238" s="2" t="s">
         <v>219</v>
       </c>
@@ -3133,7 +3147,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2">
       <c r="A239" s="3" t="s">
         <v>225</v>
       </c>
@@ -3141,7 +3155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2">
       <c r="A240" s="2" t="s">
         <v>209</v>
       </c>
@@ -3149,7 +3163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2">
       <c r="A241" s="3" t="s">
         <v>222</v>
       </c>
@@ -3157,7 +3171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2">
       <c r="A242" s="2" t="s">
         <v>258</v>
       </c>
@@ -3165,7 +3179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2">
       <c r="A243" s="3" t="s">
         <v>237</v>
       </c>
@@ -3173,7 +3187,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2">
       <c r="A244" s="2" t="s">
         <v>135</v>
       </c>
@@ -3181,7 +3195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2">
       <c r="A245" s="3" t="s">
         <v>39</v>
       </c>
@@ -3189,7 +3203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2">
       <c r="A246" s="2" t="s">
         <v>40</v>
       </c>
@@ -3197,7 +3211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2">
       <c r="A247" s="3" t="s">
         <v>245</v>
       </c>
@@ -3205,7 +3219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2">
       <c r="A248" s="2" t="s">
         <v>41</v>
       </c>
@@ -3213,7 +3227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2">
       <c r="A249" s="3" t="s">
         <v>22</v>
       </c>
@@ -3221,7 +3235,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2">
       <c r="A250" s="2" t="s">
         <v>228</v>
       </c>
@@ -3229,7 +3243,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2">
       <c r="A251" s="3" t="s">
         <v>259</v>
       </c>
@@ -3237,7 +3251,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2">
       <c r="A252" s="2" t="s">
         <v>262</v>
       </c>
@@ -3245,7 +3259,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2">
       <c r="A253" s="3" t="s">
         <v>263</v>
       </c>
@@ -3253,7 +3267,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2">
       <c r="A254" s="2" t="s">
         <v>264</v>
       </c>
@@ -3261,7 +3275,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2">
       <c r="A255" s="3" t="s">
         <v>265</v>
       </c>
@@ -3269,7 +3283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2">
       <c r="A256" s="2" t="s">
         <v>266</v>
       </c>
@@ -3277,7 +3291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2">
       <c r="A257" s="4" t="s">
         <v>270</v>
       </c>
@@ -3285,7 +3299,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2">
       <c r="A258" s="2" t="s">
         <v>267</v>
       </c>
@@ -3293,15 +3307,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A259" s="5" t="s">
+    <row r="259" spans="1:2">
+      <c r="A259" s="6" t="s">
         <v>268</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2">
       <c r="A260" s="2" t="s">
         <v>269</v>
       </c>
@@ -3309,7 +3323,32 @@
         <v>251</v>
       </c>
     </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B262" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:B260"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
